--- a/Practica2_Fiabilidad.xlsx
+++ b/Practica2_Fiabilidad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaime/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E51C56-ED2E-1D41-8D80-597737FE707F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FF2401-CD80-F248-8048-21FB0F289678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="24980" windowHeight="16680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="a) Indicadores básicos" sheetId="1" r:id="rId1"/>
@@ -387,7 +387,6 @@
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -395,15 +394,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -424,15 +414,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -450,12 +431,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1206,376 +1206,381 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9">
-        <v>1</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="A5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
         <v>2</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="5">
         <v>3</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="5">
         <v>4</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="5">
         <v>5</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="5">
         <v>6</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="5">
         <v>7</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="5">
         <v>8</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="5">
         <v>9</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="5">
         <v>10</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="5">
         <v>11</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="5">
         <v>12</v>
       </c>
-      <c r="N5" s="9">
+      <c r="N5" s="5">
         <v>13</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="5">
         <v>14</v>
       </c>
-      <c r="P5" s="9">
+      <c r="P5" s="5">
         <v>15</v>
       </c>
-      <c r="Q5" s="9">
+      <c r="Q5" s="5">
         <v>16</v>
       </c>
-      <c r="R5" s="9">
+      <c r="R5" s="5">
         <v>17</v>
       </c>
-      <c r="S5" s="9">
+      <c r="S5" s="5">
         <v>18</v>
       </c>
-      <c r="T5" s="9">
+      <c r="T5" s="5">
         <v>19</v>
       </c>
-      <c r="U5" s="9">
+      <c r="U5" s="5">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="11">
-        <v>1</v>
-      </c>
-      <c r="C6" s="11">
-        <v>1</v>
-      </c>
-      <c r="D6" s="11">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12">
-        <v>0</v>
-      </c>
-      <c r="F6" s="12">
-        <v>0</v>
-      </c>
-      <c r="G6" s="11">
-        <v>1</v>
-      </c>
-      <c r="H6" s="11">
-        <v>1</v>
-      </c>
-      <c r="I6" s="11">
-        <v>1</v>
-      </c>
-      <c r="J6" s="11">
-        <v>1</v>
-      </c>
-      <c r="K6" s="12">
-        <v>0</v>
-      </c>
-      <c r="L6" s="11">
-        <v>1</v>
-      </c>
-      <c r="M6" s="11">
-        <v>1</v>
-      </c>
-      <c r="N6" s="12">
-        <v>0</v>
-      </c>
-      <c r="O6" s="12">
-        <v>0</v>
-      </c>
-      <c r="P6" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="11">
-        <v>1</v>
-      </c>
-      <c r="R6" s="11">
-        <v>1</v>
-      </c>
-      <c r="S6" s="11">
-        <v>1</v>
-      </c>
-      <c r="T6" s="11">
-        <v>1</v>
-      </c>
-      <c r="U6" s="12">
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>1</v>
+      </c>
+      <c r="M6" s="7">
+        <v>1</v>
+      </c>
+      <c r="N6" s="8">
+        <v>0</v>
+      </c>
+      <c r="O6" s="8">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="7">
+        <v>1</v>
+      </c>
+      <c r="R6" s="7">
+        <v>1</v>
+      </c>
+      <c r="S6" s="7">
+        <v>1</v>
+      </c>
+      <c r="T6" s="7">
+        <v>1</v>
+      </c>
+      <c r="U6" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="8">
         <f t="shared" ref="B7:U7" si="0">1-B6</f>
         <v>0</v>
       </c>
-      <c r="C7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="D7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E7" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F7" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N7" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="O7" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="P7" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="Q7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T7" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U7" s="13">
+      <c r="C7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F7" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N7" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="O7" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="P7" s="9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U7" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="5"/>
+      <c r="C10" s="24"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="20">
         <f>SUM(B6:U6)</f>
         <v>13</v>
       </c>
-      <c r="C11" s="4"/>
+      <c r="C11" s="20"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="20">
         <f>SUM(B7:U7)</f>
         <v>7</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="20"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="17">
         <f>B11/(B11+B12)</f>
         <v>0.65</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="17"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="20">
         <f>SUMPRODUCT((B6:T6=1)*(C6:U6=0))</f>
         <v>4</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="20"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="21">
         <f>IFERROR(B11/B14,0)</f>
         <v>3.25</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="21"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="21">
         <f>B15+B17</f>
         <v>5</v>
       </c>
-      <c r="C16" s="2"/>
+      <c r="C16" s="21"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="21">
         <f>IFERROR(B12/B14,0)</f>
         <v>1.75</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" s="21"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="17">
         <f>B12/(B11+B12)</f>
         <v>0.35</v>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="17"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="25" t="s">
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A3:V3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="E21:G21"/>
@@ -1584,11 +1589,6 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="A3:V3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1612,340 +1612,340 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="11">
         <v>62</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G3" s="25"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="F5" s="19" t="s">
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="F5" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="13">
         <v>6.9444444444444501E-4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="13">
         <v>4.1666666666666699E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="18">
-        <v>1</v>
-      </c>
-      <c r="C7" s="18" t="s">
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="14">
         <f t="shared" ref="D7:D16" si="0">IF(B7="",0,B7*VLOOKUP(C7,$F$5:$G$8,2,FALSE()))</f>
         <v>4.1666666666666699E-2</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="11">
         <v>300</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="14">
         <f t="shared" si="0"/>
         <v>0.20833333333333351</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="13">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="11">
         <v>2</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="11">
         <v>50</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="14">
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="11">
         <v>20</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="14">
         <f t="shared" si="0"/>
         <v>1.38888888888889E-2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="11">
         <v>24</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="14">
         <f t="shared" si="0"/>
         <v>1.0000000000000009</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="11">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="14">
         <f t="shared" si="0"/>
         <v>2.083333333333335E-3</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="11">
         <v>2</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="11">
         <v>2</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="14">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18" t="s">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="21">
+      <c r="D16" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="1">
         <f>B3*VLOOKUP(C3,$F$5:$G$8,2,FALSE())</f>
         <v>434</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="1">
         <f>SUM(D7:D16)</f>
         <v>369.26597222222227</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="1">
         <f>B21-B22</f>
         <v>64.734027777777726</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="2">
         <f>B23/B21</f>
         <v>0.14915674603174592</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="3">
         <f>COUNT(B7:B16)</f>
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="1">
         <f>IFERROR(B23/B25,0)</f>
         <v>7.1926697530864141</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="1">
         <f>B26+B28</f>
         <v>48.222222222222221</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="1">
         <f>IFERROR(B22/B25,0)</f>
         <v>41.029552469135808</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="2">
         <f>B22/B21</f>
         <v>0.85084325396825411</v>
       </c>
@@ -1976,193 +1976,193 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="15">
         <f>'b) Periodo de control'!B29</f>
         <v>0.85084325396825411</v>
       </c>
-      <c r="C3" s="23"/>
+      <c r="C3" s="16"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="23"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="16"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="14">
         <f>IF(B4="",B3,B4)</f>
         <v>0.85084325396825411</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="18">
-        <v>0</v>
-      </c>
-      <c r="B8" s="21">
+      <c r="A8" s="11">
+        <v>0</v>
+      </c>
+      <c r="B8" s="14">
         <f t="shared" ref="B8:B18" si="0">EXP(-$B$5*A8)</f>
         <v>1</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="14">
         <f t="shared" ref="C8:C18" si="1">1-B8</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="18">
-        <v>1</v>
-      </c>
-      <c r="B9" s="21">
+      <c r="A9" s="11">
+        <v>1</v>
+      </c>
+      <c r="B9" s="14">
         <f t="shared" si="0"/>
         <v>0.42705466453108282</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="14">
         <f t="shared" si="1"/>
         <v>0.57294533546891713</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="18">
+      <c r="A10" s="11">
         <v>2</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="14">
         <f t="shared" si="0"/>
         <v>0.18237568649775565</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="14">
         <f t="shared" si="1"/>
         <v>0.81762431350224429</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="18">
+      <c r="A11" s="11">
         <v>3</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="14">
         <f t="shared" si="0"/>
         <v>7.7884387615924977E-2</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="14">
         <f t="shared" si="1"/>
         <v>0.92211561238407502</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="18">
+      <c r="A12" s="11">
         <v>4</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="14">
         <f t="shared" si="0"/>
         <v>3.3260891025527657E-2</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="14">
         <f t="shared" si="1"/>
         <v>0.96673910897447235</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="18">
+      <c r="A13" s="11">
         <v>5</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="14">
         <f t="shared" si="0"/>
         <v>1.4204218658911614E-2</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="14">
         <f t="shared" si="1"/>
         <v>0.98579578134108836</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="18">
+      <c r="A14" s="11">
         <v>6</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="14">
         <f t="shared" si="0"/>
         <v>6.0659778343076483E-3</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="14">
         <f t="shared" si="1"/>
         <v>0.99393402216569238</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="18">
+      <c r="A15" s="11">
         <v>7</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="14">
         <f t="shared" si="0"/>
         <v>2.5905041290832354E-3</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="14">
         <f t="shared" si="1"/>
         <v>0.99740949587091676</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="18">
+      <c r="A16" s="11">
         <v>8</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="14">
         <f t="shared" si="0"/>
         <v>1.1062868718120262E-3</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="14">
         <f t="shared" si="1"/>
         <v>0.99889371312818798</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="18">
+      <c r="A17" s="11">
         <v>9</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="14">
         <f t="shared" si="0"/>
         <v>4.7244496891682598E-4</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="14">
         <f t="shared" si="1"/>
         <v>0.99952755503108315</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="18">
+      <c r="A18" s="11">
         <v>10</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="14">
         <f t="shared" si="0"/>
         <v>2.0175982771017284E-4</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="14">
         <f t="shared" si="1"/>
         <v>0.9997982401722898</v>
       </c>
